--- a/utility data/water_provider_tracking.xlsx
+++ b/utility data/water_provider_tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu.sharepoint.com/sites/CEAE-HUB/Shared Documents/General/1 Projects/2025 Elasticity and Rate Structures CWCB/Jade/hub-gra-cwcb-rates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu.sharepoint.com/sites/CEAE-HUB/Shared Documents/General/1 Projects/2025 Elasticity and Rate Structures CWCB/Jade/hub-gra-cwcb-rates/utility data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_1465E2473891C05EEEDE154F51EB95AB88A394F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2248E1C-BEF1-49E2-90A4-1816847FDA55}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="11_1465E2473891C05EEEDE154F51EB95AB88A394F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D61873C-EB56-47A7-AC3F-50EC93F7CB64}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28965" yWindow="7545" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Service Area</t>
   </si>
@@ -66,20 +66,604 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>9/22 -- rec'd spreadsheet over email</t>
-  </si>
-  <si>
     <t>Fort Collins, City of</t>
   </si>
   <si>
     <t>https://gisweb.fcgov.com/HTML5Viewer/index.html?Viewer=Utility%20Districts</t>
+  </si>
+  <si>
+    <t>Denver Water</t>
+  </si>
+  <si>
+    <t>Boulder, City of</t>
+  </si>
+  <si>
+    <t>Alice Conovitz</t>
+  </si>
+  <si>
+    <t>aconovitz@fcgov.com</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Also working on an "Intervention Plan" to determine how well current customers understand and react to their water bills -- see </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Westminster_Intervention_Plan_Updated - db.docx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for details (and, related, see WRF Project 5265)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.waterrf.org/research/projects/evaluating-changes-peak-water-demand-and-how-may-affect-choice-design-management</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WAITING</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[ 12/17/25 ] email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+verified that Alice is still planning to get the account-level data to us
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 10/07-08/25 ] email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+requested account-level data
+received confirmation that the data will be requested
+clarified range of years
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 10/03/25 ] received via email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2001-2022_BillingData_Res_CISDownload.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>billing data aggregrated by rate code (which was readility accessible)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RECEIVED</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[ 10/03/25 ] received via email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2010-2024 Rate Sheets (W,WW,SW).pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Water_Rates_History_MetaData_Extract.xlsx</t>
+    </r>
+  </si>
+  <si>
+    <t>Greeley, City of</t>
+  </si>
+  <si>
+    <t>Longmont, City of</t>
+  </si>
+  <si>
+    <t>Dena Egenhoff</t>
+  </si>
+  <si>
+    <t>dena.egenhoff@greeleygov.com</t>
+  </si>
+  <si>
+    <t>met at WaterWise Symposium in Sept 2025, planned to reach out to contact</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RECEIVED</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[ 09/22/25 ] received via email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CoW Water Rates 2010-2025.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 10/22/25 ] via email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">additional context in the email body, captured in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Westminster Email Context.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RECEIVED</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[ 10/22/25 ] uploaded to OneDrive folder:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CoW 20XX Consumption.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data workbooks for each year 2015-2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CoW Billing Data 102225.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">aggregated data summary &amp; additional context (filled out provided template)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ 10/22/25 ] via email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>additional context in the email body, captured in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Westminster Email Context.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t>connection established via Nick Guthro</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">already have Comprehensive Annual Reports for 2009-2022 -- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>need 2023-2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20XX-comprehensive-annual-financial-report.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">already have rates for 2010-2024 -- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>need fixed fees</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Historical Block Rates.xlsx</t>
+    </r>
+  </si>
+  <si>
+    <t>Krystle Morey</t>
+  </si>
+  <si>
+    <t>moreyk@bouldercolorado.gov</t>
+  </si>
+  <si>
+    <t>existing data obtained through public records request</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +681,60 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -131,12 +769,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="16">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -161,8 +800,121 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.59999389629810485"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.59999389629810485"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical style="thin">
+          <color theme="0"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="0"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{C98E5B7E-F1D3-498D-B402-0478A479C4A2}">
+      <tableStyleElement type="headerRow" dxfId="15"/>
+    </tableStyle>
+    <tableStyle name="TableStyleMedium14 2" pivot="0" count="7" xr9:uid="{4B036786-7E27-4530-BA70-6EE044EE26D5}">
+      <tableStyleElement type="wholeTable" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="totalRow" dxfId="12"/>
+      <tableStyleElement type="firstColumn" dxfId="11"/>
+      <tableStyleElement type="lastColumn" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -192,7 +944,7 @@
     <tableColumn id="9" xr3:uid="{EF02BA34-E019-4305-B4B4-744EB193649C}" name="Notes" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{5641FC13-D502-48F7-BFC0-9D2046BC3962}" name="Column1"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -459,19 +1211,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="30.1796875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="40.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.1796875" style="1" customWidth="1"/>
     <col min="8" max="8" width="41.7265625" style="1" customWidth="1"/>
     <col min="9" max="9" width="1.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,7 +1253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -514,20 +1267,100 @@
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D38" xr:uid="{9888FCF0-01AD-4C6E-A04B-5B6D75E0BE9F}">
       <formula1>"Yes - will use,Yes - won't use,Yes - TBD,No"</formula1>
     </dataValidation>
@@ -535,24 +1368,19 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{4992CF4A-6B83-44EA-9FA3-AF0B26A0191E}"/>
     <hyperlink ref="H3" r:id="rId2" xr:uid="{905995A0-5CFF-40F3-8BE6-D25683E57C38}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{2963ED67-D771-440C-900E-CC7A98DF1DFB}"/>
+    <hyperlink ref="J2" r:id="rId4" xr:uid="{38C0D11D-B0C6-450E-B874-D20B9D226432}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{58C0349B-2814-4E02-94DE-826DF68B51BB}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{EF02C027-8E1B-4CDA-B993-BBCA9A95F3ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="68738bc9-97b6-4aea-9722-c8130ccafb9b" xsi:nil="true"/>
@@ -563,9 +1391,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095E869ECB1E35142B7986647353A6071" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd59a79325bdce54e5e21e2629eabd4a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e0f7cf-9242-4a2b-99ce-72db65c8030e" xmlns:ns3="68738bc9-97b6-4aea-9722-c8130ccafb9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fce0723309a65e62c1e02d4838c24021" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095E869ECB1E35142B7986647353A6071" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4323567e9d5277c52290584e94a0ace5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e0f7cf-9242-4a2b-99ce-72db65c8030e" xmlns:ns3="68738bc9-97b6-4aea-9722-c8130ccafb9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f99e310bc6b3a9b0fa48fe2735459f73" ns2:_="" ns3:_="">
     <xsd:import namespace="43e0f7cf-9242-4a2b-99ce-72db65c8030e"/>
     <xsd:import namespace="68738bc9-97b6-4aea-9722-c8130ccafb9b"/>
     <xsd:element name="properties">
@@ -804,15 +1632,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D20F70E-50C9-46EB-94B2-56B346E330D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1AE61C6-2381-44F1-86F1-81432D8D0A45}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -823,8 +1652,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688E4651-C12B-402D-B8C9-571CAF7AD4B7}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B9F759-4211-442A-AC45-6761E83CE30A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -840,4 +1669,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D20F70E-50C9-46EB-94B2-56B346E330D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>